--- a/data/output/evaluasi_11.xlsx
+++ b/data/output/evaluasi_11.xlsx
@@ -8,11 +8,28 @@
   </bookViews>
   <sheets>
     <sheet name="1100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1172" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1107" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="1174" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1175" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="1111" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="1118" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1113" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1103" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1104" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1110" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1111" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1114" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1118" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1173" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1101" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1102" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="1106" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="1108" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="1116" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="1171" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="1115" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="1117" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="1172" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="1175" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="1109" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="1112" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +497,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>128.940633716271</v>
+        <v>113.4871708939969</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -489,7 +506,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -508,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-9.823597758129212</v>
+        <v>63.02615389036321</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -517,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -536,7 +553,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.804752442339</v>
+        <v>224.1419922120065</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -545,7 +562,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -564,7 +581,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.17146123227691</v>
+        <v>36.1929976693684</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -573,7 +590,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -588,20 +605,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>125.885773952378</v>
+        <v>44.21108809737466</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -616,20 +633,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-7.691812887423676</v>
+        <v>107.1720147203644</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>adhk_pi_q1-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -644,20 +661,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>54.81581313846237</v>
+        <v>130.1891484291664</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -672,20 +689,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8781412543782997</v>
+        <v>77.40743331682158</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25 vs distribusi_pi_q1-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -704,16 +721,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.5584674023612606</v>
+        <v>41.26157400950639</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q1-25 vs distribusi_net_ekspor_q1-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -732,16 +749,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-3.697718529517947</v>
+        <v>12.43908358863264</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -756,20 +773,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.7570878522542129</v>
+        <v>-11.4680771421894</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+          <t>adhk_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -788,16 +805,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.7570878522542129</v>
+        <v>-5.031793163746385</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -812,20 +829,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.127586466397305</v>
+        <v>1.01129586841603</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -840,20 +857,2720 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-41.70741100800628</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.3820455902225544</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Growth berlawanan arah</t>
+      <c r="D16" t="n">
+        <v>29.87673697931512</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.4815668484313012</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-9.831434483658287</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3.238399377711832</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3.900290172705127</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q1-25 vs y-on-y_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.47497718681349</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.978491541661997</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3.523277143931005</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q2-25 vs y-on-y_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4.068296167536801</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.740152309592506</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.33141421310564</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.0362946466422112</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.79726551231595</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>11</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.060653736658058</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3.900290172705127</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q1-25 vs c-to-c_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>11</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3.978491541661997</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.748406320722903</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q2-25 vs c-to-c_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3.855413808524002</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25 vs c-to-c_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-2.740152309592506</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4.747056650635282</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3.187494562144356</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.79726551231595</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.007518088472252</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aceh</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-1.026648346090183</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3630217621412802</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6465349173275576</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3705031805588231</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.32603711867792</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.129172428424306</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5302836168648123</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Langsa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.4128668831103925</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Langsa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.681775437727634</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Langsa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.007363483612045777</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0387606242053015</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.636482600002472</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-10.48219187298488</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.460558785714859</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-8.431657244599627</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Simeulue</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7688827155841276</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2710668788759332</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.926522741468894</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>23.36390170041172</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1273670454791741</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Singkil</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4802281118081422</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.852733623057513</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.828659467411334</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.950357347438417</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.585491473778511</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.818787282543384</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.298097316203788</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.198137225255818</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.07379573202813175</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-11.96374972588327</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.19517269038993</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Besar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.0467491686304017</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.776104347520487</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-14.85484100724531</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.9239664578529453</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.22764270219068</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.0392190353663273</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.206690725614894</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.689336124862286</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9294096442696712</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.9524510601638342</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.129770438449846</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.205496461464289</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.675900872819278</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09156814184602119</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.071157846756851</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.865818582871464</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-10.77226020161791</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5530651914155268</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-13.48091042835263</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nagan Raya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.5299948286273554</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.600150813484766</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.7579063215491398</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.389225765590524</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.6450456740850209</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.031613948645664</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bener Meriah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.393343179042972</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -868,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +3622,304 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.013787500545237</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.962768633435115</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2282555527334351</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.685283230419119</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.34310133100008</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-7.952572556994673</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.6179845394011912</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3006986544238959</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.172597329229819</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1172</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -914,20 +3929,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3117.122792418</v>
+        <v>-2.423683885430295</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -942,20 +3957,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2256.69713331</v>
+        <v>-1.027605861458551</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -970,20 +3985,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.8968662537528975</v>
+        <v>0.2732568637680236</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -998,20 +4013,522 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1464708500102882</v>
+        <v>0.06390140310761375</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02738106330514442</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Sabang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2068017929298754</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.037191538919474</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.802748897779958</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.535716128179175</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.311157292675936</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7267362018079574</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-7.126608213849544</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2826419096332276</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pidie</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.099955495841645</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9.065175321121508</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.746713134091963</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-6.896577815942879</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +4543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,16 +4593,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3235.534461972</v>
+        <v>2.584346514121289</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1100,20 +4617,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-186083.8607274001</v>
+        <v>0.491676165479928</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1128,20 +4645,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22614.714605578</v>
+        <v>-3.293232475950728</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1156,20 +4673,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32612.99765499984</v>
+        <v>-0.9758190959327827</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1184,20 +4701,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.580865332444976</v>
+        <v>1.97185451335054</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1212,20 +4729,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7882997159036472</v>
+        <v>8.277211989043733</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1240,20 +4757,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.31761417719512</v>
+        <v>0.4515582290265811</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1268,20 +4785,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.241831630709711</v>
+        <v>-2.301847979068106</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1296,20 +4813,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05278836380854837</v>
+        <v>-1.28945100299123</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1324,20 +4841,104 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.6679404163099165</v>
+        <v>5.555334854912967</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5210286136960511</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.690011607195602</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.542448030984027</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1389,253 +4990,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-185490.0855650001</v>
+        <v>-2.593763117533948</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1166008762705384</v>
+        <v>0.5254296222337472</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1166008762705384</v>
+        <v>-4.204745940405775</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1584124590613014</v>
+        <v>9.702478722408928</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.46599050819706</v>
+        <v>3.78598591146312</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05482238291252009</v>
+        <v>4.365639779005321</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.967354740612168</v>
+        <v>2.024905984287716</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.05117267283105685</v>
+        <v>7.658336974904763</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1175</v>
+        <v>1113</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kota Subulussalam</t>
+          <t>Kabupaten Gayo Lues</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.537409818295405</v>
+        <v>-2.579242351246782</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q3-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1650,7 +5251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,29 +5288,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Aceh Utara</t>
+          <t>Kabupaten Aceh Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.01961619212370648</v>
+        <v>-0.7936622361817182</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-4.238977979641552</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.469506645790094</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5691972125279754</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3792884352473877</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1724,7 +5437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,29 +5474,811 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pidie Jaya</t>
+          <t>Kabupaten Aceh Tenggara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.862945731618579</v>
+        <v>-4.988606622680017</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.690525132316756</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.96566489215371</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3692700121848602</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.990340428344263</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.01798963615179</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.214855468738683</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tenggara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-4.579252556989021</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.31190731911465</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-27.81183910854585</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4732140415778343</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.673892879976208</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.40014577665824</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.491481230075764</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bireuen</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.966346159506817</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.283150341175821</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.6179639123412</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.233789265525095</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.217597777387478</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.404197981685769</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.589347644452253</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-8.244059488009759</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.87168592992992</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.261570816275394</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_11.xlsx
+++ b/data/output/evaluasi_11.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
